--- a/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_36.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1859182.113950345</v>
+        <v>1851285.663886919</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7154817.030747602</v>
+        <v>7154817.0307476</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7154817.030747602</v>
+        <v>7154817.0307476</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1421810.501097732</v>
+        <v>1421810.501097731</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1421810.501097732</v>
+        <v>1421810.501097731</v>
       </c>
     </row>
     <row r="11">
@@ -672,7 +672,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>36.71585008894188</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -723,7 +723,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>140.0236240682209</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -742,16 +742,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>12.84202976864526</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>385</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>305.214484270644</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>192.3498461705186</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1015,16 +1015,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>385</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>371.5681244750684</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>148.6880250402009</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>385</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>385</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>107.8044165526436</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>184.2505648441361</v>
       </c>
       <c r="H11" t="n">
         <v>183.0096587035274</v>
@@ -1434,7 +1434,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>291.8106252399262</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1568,10 +1568,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1650,13 +1650,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S14" t="n">
         <v>269.8481678023229</v>
       </c>
       <c r="T14" t="n">
-        <v>361.6755817285639</v>
+        <v>367.1687742856838</v>
       </c>
       <c r="U14" t="n">
         <v>424.2212965486107</v>
@@ -1799,13 +1799,13 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>25.87859882829446</v>
+        <v>31.37179138541422</v>
       </c>
       <c r="S17" t="n">
         <v>269.8481678023229</v>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G20" t="n">
-        <v>184.2505648441361</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H20" t="n">
         <v>183.0096587035274</v>
@@ -2145,7 +2145,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>286.3174326828064</v>
+        <v>291.8106252399262</v>
       </c>
     </row>
     <row r="21">
@@ -2322,13 +2322,13 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>179.3632896068686</v>
+        <v>184.8564821639885</v>
       </c>
       <c r="F23" t="n">
         <v>179.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>184.2505648441361</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H23" t="n">
         <v>183.0096587035274</v>
@@ -2471,22 +2471,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>3.77112610161862</v>
@@ -2516,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>70.00397654534778</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2537,10 +2537,10 @@
         <v>1.372809838709685</v>
       </c>
       <c r="X25" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2571,7 +2571,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>275.3413603594427</v>
       </c>
       <c r="T26" t="n">
         <v>361.6755817285639</v>
@@ -2753,10 +2753,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>342.1496093272373</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>25.87859882829446</v>
+        <v>31.37179138541422</v>
       </c>
       <c r="S29" t="n">
         <v>269.8481678023229</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S32" t="n">
         <v>269.8481678023229</v>
@@ -3227,10 +3227,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T35" t="n">
         <v>236.6755817285639</v>
@@ -3321,7 +3321,7 @@
         <v>299.2212965486107</v>
       </c>
       <c r="V35" t="n">
-        <v>283.8164155522384</v>
+        <v>279.8510241668239</v>
       </c>
       <c r="W35" t="n">
         <v>288.3734759809475</v>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
         <v>11.09991244551929</v>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>197.2737972923793</v>
+        <v>259.9515598178218</v>
       </c>
       <c r="S36" t="n">
         <v>116.5639999646113</v>
@@ -3400,13 +3400,13 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
-        <v>64.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
         <v>82.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>132.54050197083</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>49.39139276613435</v>
@@ -3513,7 +3513,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H38" t="n">
         <v>58.00965870352741</v>
@@ -3555,7 +3555,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U38" t="n">
-        <v>299.2212965486107</v>
+        <v>303.1866879340253</v>
       </c>
       <c r="V38" t="n">
         <v>279.8510241668239</v>
@@ -3583,10 +3583,10 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>64.74007562773993</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3595,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>80.50967533902144</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H41" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>97.2343191717691</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>11.09991244551929</v>
@@ -3829,10 +3829,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3883,7 +3883,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="43">
@@ -4063,10 +4063,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -4114,10 +4114,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>432.3731429098285</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X45" t="n">
-        <v>132.54050197083</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y45" t="n">
         <v>49.39139276613435</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D2" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E2" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F2" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G2" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H2" t="n">
         <v>30.8</v>
@@ -4366,7 +4366,7 @@
         <v>336.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="C3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="D3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="E3" t="n">
-        <v>30.8</v>
+        <v>709.3902318427254</v>
       </c>
       <c r="F3" t="n">
-        <v>30.8</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="G3" t="n">
-        <v>30.8</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H3" t="n">
         <v>30.8</v>
@@ -4430,22 +4430,22 @@
         <v>795.4071048660406</v>
       </c>
       <c r="T3" t="n">
-        <v>406.5182159771517</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U3" t="n">
-        <v>98.22075711791538</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V3" t="n">
-        <v>83.56351753052128</v>
+        <v>775.1254966143025</v>
       </c>
       <c r="W3" t="n">
-        <v>50.86337317715914</v>
+        <v>742.4253522609404</v>
       </c>
       <c r="X3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="Y3" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
     </row>
     <row r="4">
@@ -4455,25 +4455,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>804.3768145245806</v>
+        <v>860.6897953616551</v>
       </c>
       <c r="C4" t="n">
-        <v>804.3768145245806</v>
+        <v>986.6918011800909</v>
       </c>
       <c r="D4" t="n">
-        <v>804.3768145245806</v>
+        <v>1100.010945305091</v>
       </c>
       <c r="E4" t="n">
-        <v>804.3768145245806</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="F4" t="n">
-        <v>804.3768145245806</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="G4" t="n">
-        <v>957.7833804114658</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="H4" t="n">
-        <v>957.7833804114658</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="I4" t="n">
         <v>1178.916259347549</v>
@@ -4485,22 +4485,22 @@
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M4" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O4" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P4" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q4" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
@@ -4509,22 +4509,22 @@
         <v>68.05025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>234.9039126024231</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="U4" t="n">
-        <v>481.4551052407097</v>
+        <v>314.6014477324597</v>
       </c>
       <c r="V4" t="n">
-        <v>481.4551052407097</v>
+        <v>314.6014477324597</v>
       </c>
       <c r="W4" t="n">
-        <v>653.3460235003871</v>
+        <v>486.4923659921371</v>
       </c>
       <c r="X4" t="n">
-        <v>804.3768145245806</v>
+        <v>637.5231570163306</v>
       </c>
       <c r="Y4" t="n">
-        <v>804.3768145245806</v>
+        <v>748.9324576953629</v>
       </c>
     </row>
     <row r="5">
@@ -4558,19 +4558,19 @@
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="K5" t="n">
-        <v>411.9499999999999</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>777.6999999999999</v>
+        <v>1158.85</v>
       </c>
       <c r="M5" t="n">
         <v>1158.85</v>
       </c>
       <c r="N5" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="O5" t="n">
         <v>1540</v>
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C6" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D6" t="n">
-        <v>30.8</v>
+        <v>702.8967456696003</v>
       </c>
       <c r="E6" t="n">
-        <v>30.8</v>
+        <v>702.8967456696003</v>
       </c>
       <c r="F6" t="n">
-        <v>30.8</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="G6" t="n">
         <v>30.8</v>
@@ -4658,31 +4658,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>862.6434684666581</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>473.7545795777692</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T6" t="n">
-        <v>98.43324172416462</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U6" t="n">
-        <v>98.22075711791538</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>83.56351753052128</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W6" t="n">
-        <v>50.86337317715914</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X6" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y6" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>701.4985197772105</v>
+        <v>735.5658222069326</v>
       </c>
       <c r="C7" t="n">
-        <v>701.4985197772105</v>
+        <v>861.5678280253684</v>
       </c>
       <c r="D7" t="n">
-        <v>701.4985197772105</v>
+        <v>974.8869721503685</v>
       </c>
       <c r="E7" t="n">
-        <v>701.4985197772105</v>
+        <v>1092.715876361782</v>
       </c>
       <c r="F7" t="n">
-        <v>701.4985197772105</v>
+        <v>1217.076848953717</v>
       </c>
       <c r="G7" t="n">
-        <v>701.4985197772105</v>
+        <v>1370.483414840602</v>
       </c>
       <c r="H7" t="n">
-        <v>847.4189464745974</v>
+        <v>1540</v>
       </c>
       <c r="I7" t="n">
-        <v>1068.55182541068</v>
+        <v>1540</v>
       </c>
       <c r="J7" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
@@ -4743,25 +4743,25 @@
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T7" t="n">
-        <v>256.125934252978</v>
+        <v>30.8</v>
       </c>
       <c r="U7" t="n">
-        <v>502.6771268912646</v>
+        <v>30.8</v>
       </c>
       <c r="V7" t="n">
-        <v>701.4985197772105</v>
+        <v>189.4774745777372</v>
       </c>
       <c r="W7" t="n">
-        <v>701.4985197772105</v>
+        <v>361.3683928374146</v>
       </c>
       <c r="X7" t="n">
-        <v>701.4985197772105</v>
+        <v>512.3991838616081</v>
       </c>
       <c r="Y7" t="n">
-        <v>701.4985197772105</v>
+        <v>623.8084845406404</v>
       </c>
     </row>
     <row r="8">
@@ -4795,16 +4795,16 @@
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="K8" t="n">
+        <v>411.9499999999999</v>
+      </c>
+      <c r="L8" t="n">
         <v>793.0999999999999</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1158.85</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1540</v>
       </c>
       <c r="N8" t="n">
         <v>1540</v>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.8</v>
+        <v>746.9995952961838</v>
       </c>
       <c r="C9" t="n">
-        <v>30.8</v>
+        <v>382.2522089875785</v>
       </c>
       <c r="D9" t="n">
         <v>30.8</v>
@@ -4904,22 +4904,22 @@
         <v>970.2346453614745</v>
       </c>
       <c r="T9" t="n">
-        <v>581.3457564725855</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U9" t="n">
-        <v>192.4568675836966</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>83.56351753052128</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>50.86337317715914</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X9" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>30.8</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1098.9273116332</v>
+        <v>812.9599956093143</v>
       </c>
       <c r="C10" t="n">
-        <v>1098.9273116332</v>
+        <v>812.9599956093143</v>
       </c>
       <c r="D10" t="n">
-        <v>1098.9273116332</v>
+        <v>812.9599956093143</v>
       </c>
       <c r="E10" t="n">
-        <v>1098.9273116332</v>
+        <v>833.4224078195303</v>
       </c>
       <c r="F10" t="n">
-        <v>1098.9273116332</v>
+        <v>957.7833804114658</v>
       </c>
       <c r="G10" t="n">
-        <v>1098.9273116332</v>
+        <v>957.7833804114658</v>
       </c>
       <c r="H10" t="n">
-        <v>1098.9273116332</v>
+        <v>957.7833804114658</v>
       </c>
       <c r="I10" t="n">
-        <v>1098.9273116332</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="J10" t="n">
-        <v>1460.011052285652</v>
+        <v>1540</v>
       </c>
       <c r="K10" t="n">
         <v>1540</v>
       </c>
       <c r="L10" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P10" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R10" t="n">
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>218.8756791588049</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="U10" t="n">
-        <v>465.4268717970915</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="V10" t="n">
-        <v>664.2482646830374</v>
+        <v>266.8716479801191</v>
       </c>
       <c r="W10" t="n">
-        <v>836.1391829427148</v>
+        <v>438.7625662397965</v>
       </c>
       <c r="X10" t="n">
-        <v>987.1699739669083</v>
+        <v>589.7933572639899</v>
       </c>
       <c r="Y10" t="n">
-        <v>987.1699739669083</v>
+        <v>701.2026579430222</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C11" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D11" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E11" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F11" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G11" t="n">
         <v>266.2182411146742</v>
@@ -5035,22 +5035,22 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>1129.300343567238</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1129.300343567238</v>
+        <v>2089.404973955146</v>
       </c>
       <c r="M11" t="n">
-        <v>1640.149172296173</v>
+        <v>2600.253802684082</v>
       </c>
       <c r="N11" t="n">
-        <v>2253.369492070936</v>
+        <v>3213.474122458845</v>
       </c>
       <c r="O11" t="n">
-        <v>3206.412036092893</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>4068</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>4068</v>
@@ -5077,7 +5077,7 @@
         <v>1777.969718670473</v>
       </c>
       <c r="Y11" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="12">
@@ -5120,10 +5120,10 @@
         <v>1341.904675832448</v>
       </c>
       <c r="M12" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N12" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O12" t="n">
         <v>2264.733656412845</v>
@@ -5211,7 +5211,7 @@
         <v>425.5789893823512</v>
       </c>
       <c r="Q13" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R13" t="n">
         <v>81.36</v>
@@ -5275,13 +5275,13 @@
         <v>1182.375479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>2089.404973955146</v>
+        <v>1552.289212421678</v>
       </c>
       <c r="M14" t="n">
-        <v>2600.253802684082</v>
+        <v>2063.138041150613</v>
       </c>
       <c r="N14" t="n">
-        <v>3213.474122458845</v>
+        <v>2676.358360925376</v>
       </c>
       <c r="O14" t="n">
         <v>3629.400904947332</v>
@@ -5293,10 +5293,10 @@
         <v>4068</v>
       </c>
       <c r="R14" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S14" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T14" t="n">
         <v>3398.408544528989</v>
@@ -5345,19 +5345,19 @@
         <v>81.36</v>
       </c>
       <c r="I15" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>428.066520175299</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K15" t="n">
-        <v>840.0093362696824</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L15" t="n">
-        <v>1334.109797864882</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M15" t="n">
-        <v>1642.940339607742</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N15" t="n">
         <v>1802.941204729126</v>
@@ -5442,10 +5442,10 @@
         <v>425.5789893823512</v>
       </c>
       <c r="O16" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="P16" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q16" t="n">
         <v>81.36</v>
@@ -5482,46 +5482,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C17" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D17" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E17" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F17" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G17" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H17" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I17" t="n">
         <v>81.36</v>
       </c>
       <c r="J17" t="n">
-        <v>81.36</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>791.0663663478683</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>1698.095860917491</v>
+        <v>2089.404973955146</v>
       </c>
       <c r="M17" t="n">
-        <v>1698.095860917491</v>
+        <v>2600.253802684082</v>
       </c>
       <c r="N17" t="n">
-        <v>2311.316180692254</v>
+        <v>3213.474122458845</v>
       </c>
       <c r="O17" t="n">
-        <v>2767.812941040225</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>3629.400904947332</v>
@@ -5530,28 +5530,28 @@
         <v>4068</v>
       </c>
       <c r="R17" t="n">
-        <v>4041.860001183541</v>
+        <v>4036.311321832915</v>
       </c>
       <c r="S17" t="n">
-        <v>3769.286094312508</v>
+        <v>3763.737414961882</v>
       </c>
       <c r="T17" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U17" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V17" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W17" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X17" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y17" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="18">
@@ -5597,10 +5597,10 @@
         <v>1650.735217575307</v>
       </c>
       <c r="N18" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O18" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P18" t="n">
         <v>2600.013000882351</v>
@@ -5679,13 +5679,13 @@
         <v>425.5789893823512</v>
       </c>
       <c r="O19" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="P19" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R19" t="n">
         <v>81.36</v>
@@ -5719,19 +5719,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C20" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D20" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E20" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F20" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G20" t="n">
         <v>266.2182411146742</v>
@@ -5746,16 +5746,16 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>1182.375479385524</v>
+        <v>645.2597178520556</v>
       </c>
       <c r="L20" t="n">
-        <v>2089.404973955146</v>
+        <v>1552.289212421678</v>
       </c>
       <c r="M20" t="n">
-        <v>2600.253802684082</v>
+        <v>2063.138041150613</v>
       </c>
       <c r="N20" t="n">
-        <v>3213.474122458845</v>
+        <v>2676.358360925376</v>
       </c>
       <c r="O20" t="n">
         <v>3629.400904947332</v>
@@ -5788,7 +5788,7 @@
         <v>1777.969718670473</v>
       </c>
       <c r="Y20" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="21">
@@ -5831,13 +5831,13 @@
         <v>1341.904675832448</v>
       </c>
       <c r="M21" t="n">
-        <v>1446.910920121557</v>
+        <v>1650.735217575307</v>
       </c>
       <c r="N21" t="n">
-        <v>1802.941204729126</v>
+        <v>2006.765502182875</v>
       </c>
       <c r="O21" t="n">
-        <v>2264.733656412845</v>
+        <v>2468.557953866594</v>
       </c>
       <c r="P21" t="n">
         <v>2600.013000882351</v>
@@ -5965,10 +5965,10 @@
         <v>815.2116584470142</v>
       </c>
       <c r="E23" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F23" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G23" t="n">
         <v>266.2182411146742</v>
@@ -5980,25 +5980,25 @@
         <v>81.36</v>
       </c>
       <c r="J23" t="n">
-        <v>81.36</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>791.0663663478683</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1698.095860917491</v>
+        <v>1129.300343567238</v>
       </c>
       <c r="M23" t="n">
-        <v>2208.944689646426</v>
+        <v>1640.149172296173</v>
       </c>
       <c r="N23" t="n">
-        <v>2822.165009421189</v>
+        <v>2253.369492070936</v>
       </c>
       <c r="O23" t="n">
-        <v>3629.400904947332</v>
+        <v>3206.412036092893</v>
       </c>
       <c r="P23" t="n">
-        <v>3629.400904947332</v>
+        <v>4068</v>
       </c>
       <c r="Q23" t="n">
         <v>4068</v>
@@ -6071,10 +6071,10 @@
         <v>1650.735217575307</v>
       </c>
       <c r="N24" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O24" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P24" t="n">
         <v>2600.013000882351</v>
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>210.1692428567171</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C25" t="n">
-        <v>161.9619230102073</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D25" t="n">
-        <v>161.9619230102073</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E25" t="n">
-        <v>105.4155544880289</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F25" t="n">
-        <v>105.4155544880289</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G25" t="n">
-        <v>85.16921828446326</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H25" t="n">
+        <v>189.862369793817</v>
+      </c>
+      <c r="I25" t="n">
+        <v>237.7452487298999</v>
+      </c>
+      <c r="J25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="K25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="L25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="M25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="N25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="O25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="P25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="R25" t="n">
         <v>81.36</v>
       </c>
-      <c r="I25" t="n">
-        <v>129.2428789360829</v>
-      </c>
-      <c r="J25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="K25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="L25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="M25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="N25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="O25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="P25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>246.365532168991</v>
-      </c>
-      <c r="R25" t="n">
-        <v>246.365532168991</v>
-      </c>
       <c r="S25" t="n">
-        <v>246.365532168991</v>
+        <v>81.36</v>
       </c>
       <c r="T25" t="n">
-        <v>261.1912113277959</v>
+        <v>96.18567915880486</v>
       </c>
       <c r="U25" t="n">
-        <v>334.4924039660825</v>
+        <v>169.4868717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>360.0637968520285</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="W25" t="n">
-        <v>358.6771202472712</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X25" t="n">
-        <v>336.0067713279706</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y25" t="n">
-        <v>272.9104553184127</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="26">
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C26" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D26" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E26" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F26" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G26" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H26" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I26" t="n">
         <v>81.36</v>
@@ -6220,22 +6220,22 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>1182.375479385524</v>
+        <v>1083.858812904723</v>
       </c>
       <c r="L26" t="n">
-        <v>2089.404973955146</v>
+        <v>1990.888307474345</v>
       </c>
       <c r="M26" t="n">
-        <v>2600.253802684082</v>
+        <v>2501.73713620328</v>
       </c>
       <c r="N26" t="n">
-        <v>2767.812941040225</v>
+        <v>3114.957455978044</v>
       </c>
       <c r="O26" t="n">
-        <v>2767.812941040225</v>
+        <v>4068</v>
       </c>
       <c r="P26" t="n">
-        <v>3629.400904947332</v>
+        <v>4068</v>
       </c>
       <c r="Q26" t="n">
         <v>4068</v>
@@ -6244,25 +6244,25 @@
         <v>4041.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>3769.286094312508</v>
+        <v>3763.737414961882</v>
       </c>
       <c r="T26" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U26" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V26" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W26" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X26" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y26" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="27">
@@ -6293,28 +6293,28 @@
         <v>81.36</v>
       </c>
       <c r="I27" t="n">
-        <v>89.15487796756496</v>
+        <v>81.36</v>
       </c>
       <c r="J27" t="n">
-        <v>435.8613981428639</v>
+        <v>283.4386282495398</v>
       </c>
       <c r="K27" t="n">
-        <v>643.9799167834981</v>
+        <v>695.3814443439232</v>
       </c>
       <c r="L27" t="n">
-        <v>1138.080378378698</v>
+        <v>1189.481905939123</v>
       </c>
       <c r="M27" t="n">
-        <v>1446.910920121557</v>
+        <v>1498.312447681983</v>
       </c>
       <c r="N27" t="n">
-        <v>1802.941204729126</v>
+        <v>1854.342732289551</v>
       </c>
       <c r="O27" t="n">
-        <v>2264.733656412845</v>
+        <v>2316.13518397327</v>
       </c>
       <c r="P27" t="n">
-        <v>2600.013000882351</v>
+        <v>2651.414528442776</v>
       </c>
       <c r="Q27" t="n">
         <v>2651.414528442776</v>
@@ -6351,52 +6351,52 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C28" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D28" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E28" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F28" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G28" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H28" t="n">
-        <v>191.2490463985742</v>
+        <v>189.862369793817</v>
       </c>
       <c r="I28" t="n">
-        <v>239.1319253346571</v>
+        <v>237.7452487298999</v>
       </c>
       <c r="J28" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="K28" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="L28" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="M28" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="N28" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="O28" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="P28" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q28" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R28" t="n">
         <v>81.36</v>
@@ -6414,13 +6414,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X28" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y28" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="29">
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C29" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D29" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E29" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F29" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G29" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H29" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I29" t="n">
         <v>81.36</v>
@@ -6457,49 +6457,49 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>1182.375479385524</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L29" t="n">
-        <v>1303.921568289334</v>
+        <v>1129.300343567238</v>
       </c>
       <c r="M29" t="n">
-        <v>1814.770397018269</v>
+        <v>1640.149172296173</v>
       </c>
       <c r="N29" t="n">
-        <v>1814.770397018269</v>
+        <v>2253.369492070936</v>
       </c>
       <c r="O29" t="n">
-        <v>2767.812941040225</v>
+        <v>3206.412036092893</v>
       </c>
       <c r="P29" t="n">
-        <v>3629.400904947332</v>
+        <v>4068</v>
       </c>
       <c r="Q29" t="n">
         <v>4068</v>
       </c>
       <c r="R29" t="n">
-        <v>4041.860001183541</v>
+        <v>4036.311321832915</v>
       </c>
       <c r="S29" t="n">
-        <v>3769.286094312508</v>
+        <v>3763.737414961882</v>
       </c>
       <c r="T29" t="n">
-        <v>3403.957223879615</v>
+        <v>3398.408544528989</v>
       </c>
       <c r="U29" t="n">
-        <v>2975.450863729503</v>
+        <v>2969.902184378877</v>
       </c>
       <c r="V29" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W29" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X29" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y29" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="30">
@@ -6545,10 +6545,10 @@
         <v>1650.735217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1802.941204729126</v>
+        <v>2006.765502182875</v>
       </c>
       <c r="O30" t="n">
-        <v>2264.733656412845</v>
+        <v>2468.557953866594</v>
       </c>
       <c r="P30" t="n">
         <v>2600.013000882351</v>
@@ -6633,7 +6633,7 @@
         <v>425.5789893823512</v>
       </c>
       <c r="Q31" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R31" t="n">
         <v>81.36</v>
@@ -6667,25 +6667,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C32" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D32" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E32" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F32" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G32" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H32" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I32" t="n">
         <v>81.36</v>
@@ -6694,49 +6694,49 @@
         <v>472.6691130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>1182.375479385524</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>2089.404973955146</v>
+        <v>1129.300343567238</v>
       </c>
       <c r="M32" t="n">
-        <v>2600.253802684082</v>
+        <v>1640.149172296173</v>
       </c>
       <c r="N32" t="n">
-        <v>3213.474122458845</v>
+        <v>2253.369492070936</v>
       </c>
       <c r="O32" t="n">
-        <v>3629.400904947332</v>
+        <v>3206.412036092893</v>
       </c>
       <c r="P32" t="n">
-        <v>3629.400904947332</v>
+        <v>4068</v>
       </c>
       <c r="Q32" t="n">
         <v>4068</v>
       </c>
       <c r="R32" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S32" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T32" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U32" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V32" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W32" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X32" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y32" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="33">
@@ -6767,16 +6767,16 @@
         <v>81.36</v>
       </c>
       <c r="I33" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J33" t="n">
-        <v>232.0371006891147</v>
+        <v>435.8613981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>643.9799167834981</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L33" t="n">
-        <v>1138.080378378698</v>
+        <v>1341.904675832448</v>
       </c>
       <c r="M33" t="n">
         <v>1446.910920121557</v>
@@ -6870,7 +6870,7 @@
         <v>425.5789893823512</v>
       </c>
       <c r="Q34" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R34" t="n">
         <v>81.36</v>
@@ -6928,25 +6928,25 @@
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>44.72</v>
+        <v>179.7320762183974</v>
       </c>
       <c r="K35" t="n">
-        <v>598.13</v>
+        <v>733.1420762183974</v>
       </c>
       <c r="L35" t="n">
-        <v>1129.18</v>
+        <v>1286.552076218397</v>
       </c>
       <c r="M35" t="n">
-        <v>1129.18</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N35" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6955,13 +6955,13 @@
         <v>2236</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V35" t="n">
         <v>1261.695493301277</v>
@@ -7031,28 +7031,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.885958457041</v>
+        <v>937.5750872192206</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513733</v>
+        <v>819.8336731135525</v>
       </c>
       <c r="T36" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V36" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W36" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X36" t="n">
-        <v>494.2632948060407</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y36" t="n">
-        <v>444.3729990826727</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="37">
@@ -7141,19 +7141,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
         <v>103.3156148520479</v>
@@ -7165,19 +7165,19 @@
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>64.92117127106515</v>
+        <v>44.72</v>
       </c>
       <c r="K38" t="n">
-        <v>618.3311712710652</v>
+        <v>598.13</v>
       </c>
       <c r="L38" t="n">
-        <v>1171.741171271065</v>
+        <v>1151.54</v>
       </c>
       <c r="M38" t="n">
-        <v>1682.59</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N38" t="n">
-        <v>2236</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="O38" t="n">
         <v>2236</v>
@@ -7198,19 +7198,19 @@
         <v>1850.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7226,19 +7226,19 @@
         <v>461.5662247731743</v>
       </c>
       <c r="D39" t="n">
-        <v>461.5662247731743</v>
+        <v>110.1140157855959</v>
       </c>
       <c r="E39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
-        <v>126.0429043828499</v>
+        <v>44.72</v>
       </c>
       <c r="I39" t="n">
         <v>44.72</v>
@@ -7299,22 +7299,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D40" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E40" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F40" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H40" t="n">
         <v>1377.480007433093</v>
@@ -7353,22 +7353,22 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y40" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H41" t="n">
         <v>44.72</v>
@@ -7402,13 +7402,13 @@
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>137.1709049473328</v>
+        <v>44.72</v>
       </c>
       <c r="K41" t="n">
-        <v>690.5809049473327</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="L41" t="n">
-        <v>1243.990904947333</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M41" t="n">
         <v>1243.990904947333</v>
@@ -7426,28 +7426,28 @@
         <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G42" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H42" t="n">
         <v>44.72</v>
@@ -7526,7 +7526,7 @@
         <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>154.1485167851398</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="43">
@@ -7590,7 +7590,7 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U43" t="n">
         <v>372.6360891248843</v>
@@ -7639,16 +7639,16 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>137.1709049473328</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>690.5809049473327</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L44" t="n">
-        <v>1243.990904947333</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M44" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N44" t="n">
         <v>1797.400904947332</v>
@@ -7694,19 +7694,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C45" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D45" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F45" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G45" t="n">
         <v>44.72</v>
@@ -7757,13 +7757,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W45" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X45" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y45" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="46">
@@ -8201,22 +8201,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>35.04300624509033</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>384.9999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>369.4444444444445</v>
+        <v>369.4444444444443</v>
       </c>
       <c r="M5" t="n">
-        <v>929.2621276423173</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>862.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>70.24786957409245</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
@@ -8438,19 +8438,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
-        <v>384.9999999999999</v>
+        <v>385</v>
       </c>
       <c r="L8" t="n">
-        <v>369.4444444444443</v>
+        <v>385</v>
       </c>
       <c r="M8" t="n">
-        <v>929.2621276423173</v>
+        <v>913.7065720867616</v>
       </c>
       <c r="N8" t="n">
-        <v>477.2489580698352</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409245</v>
@@ -8678,10 +8678,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>663.2638692218004</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,13 +8690,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>1032.917105959907</v>
+        <v>490.3759326937771</v>
       </c>
       <c r="P11" t="n">
-        <v>870.5779326741233</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8918,7 +8918,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>916.1914086561842</v>
+        <v>373.6502353900541</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,7 +8927,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>490.3759326937771</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9149,7 +9149,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
         <v>716.8751175230994</v>
@@ -9158,16 +9158,16 @@
         <v>916.1914086561842</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>531.3557083094171</v>
+        <v>490.3759326937771</v>
       </c>
       <c r="P17" t="n">
-        <v>870.5779326741233</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9389,7 +9389,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>174.3339442569695</v>
       </c>
       <c r="L20" t="n">
         <v>916.1914086561842</v>
@@ -9401,7 +9401,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>490.3759326937771</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
@@ -9623,13 +9623,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>663.2638692218004</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,13 +9638,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>885.6376630348439</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,7 +9863,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>617.3633331990579</v>
       </c>
       <c r="L26" t="n">
         <v>916.1914086561842</v>
@@ -9872,16 +9872,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>646.5006129750309</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P26" t="n">
-        <v>870.5779326741233</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,16 +10100,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>122.773827175565</v>
+        <v>663.2638692218004</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
         <v>1032.917105959907</v>
@@ -10118,7 +10118,7 @@
         <v>870.5779326741233</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,10 +10337,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>916.1914086561842</v>
+        <v>663.2638692218004</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
@@ -10349,13 +10349,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>490.3759326937771</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,28 +10571,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>35.04300624509033</v>
+        <v>171.4188408091281</v>
       </c>
       <c r="K35" t="n">
         <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>536.4141414141417</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,13 +10808,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>55.44822975121676</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
@@ -10823,7 +10823,7 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>90.65309308021877</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11045,16 +11045,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>128.4277587171436</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L41" t="n">
         <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
         <v>1036.248958069835</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>128.4277587171436</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
@@ -11291,10 +11291,10 @@
         <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>801.3851497733039</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23657,13 +23657,13 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>415.445564079015</v>
+        <v>74.66876459048729</v>
       </c>
       <c r="P16" t="n">
         <v>462.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R16" t="n">
         <v>501.6021279811511</v>
@@ -23894,7 +23894,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>415.445564079015</v>
+        <v>74.66876459048729</v>
       </c>
       <c r="P19" t="n">
         <v>462.4478973282775</v>
@@ -23903,7 +23903,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S19" t="n">
         <v>137.3734797028554</v>
@@ -24329,22 +24329,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D25" t="n">
         <v>60.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F25" t="n">
         <v>49.38285596774193</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -24374,10 +24374,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>430.8352898802502</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S25" t="n">
         <v>137.3734797028554</v>
@@ -24395,10 +24395,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="26">
@@ -24611,10 +24611,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>158.6896570983607</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24629,7 +24629,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>22.44364543010755</v>
@@ -24848,10 +24848,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -25085,10 +25085,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S34" t="n">
         <v>137.3734797028554</v>
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6326538.530966835</v>
+        <v>6326538.530966836</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7336594.241408324</v>
+        <v>7336594.241408325</v>
       </c>
     </row>
     <row r="9">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9356705.662291305</v>
+        <v>9356705.662291303</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10366761.3727328</v>
+        <v>10366761.37273279</v>
       </c>
     </row>
     <row r="12">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12425634.43776003</v>
+        <v>12425634.43776002</v>
       </c>
     </row>
     <row r="14">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15637045.89060817</v>
+        <v>15637045.89060816</v>
       </c>
     </row>
   </sheetData>
@@ -26284,10 +26284,10 @@
         <v>1069470.75223217</v>
       </c>
       <c r="G2" t="n">
+        <v>1069470.75223217</v>
+      </c>
+      <c r="H2" t="n">
         <v>1069470.752232171</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1069470.75223217</v>
       </c>
       <c r="I2" t="n">
         <v>1069470.752232171</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416947</v>
       </c>
       <c r="E4" t="n">
-        <v>445852.6895118617</v>
+        <v>448189.3974235593</v>
       </c>
       <c r="F4" t="n">
-        <v>444399.1387482318</v>
+        <v>446735.8466599294</v>
       </c>
       <c r="G4" t="n">
-        <v>442943.5821390834</v>
+        <v>445280.2900507811</v>
       </c>
       <c r="H4" t="n">
-        <v>441486.0053004215</v>
+        <v>443822.7132121191</v>
       </c>
       <c r="I4" t="n">
-        <v>440026.3936608352</v>
+        <v>442363.1015725328</v>
       </c>
       <c r="J4" t="n">
-        <v>438564.7324579426</v>
+        <v>440901.4403696403</v>
       </c>
       <c r="K4" t="n">
-        <v>437101.0067347542</v>
+        <v>439437.7146464519</v>
       </c>
       <c r="L4" t="n">
-        <v>435635.201335937</v>
+        <v>437971.9092476346</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.6773203549</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>369935.2421138714</v>
+        <v>368419.3864255556</v>
       </c>
       <c r="C6" t="n">
-        <v>507513.2222476852</v>
+        <v>505997.3665593694</v>
       </c>
       <c r="D6" t="n">
-        <v>509573.994160001</v>
+        <v>508058.1384716856</v>
       </c>
       <c r="E6" t="n">
-        <v>140404.9377203087</v>
+        <v>138068.2298086106</v>
       </c>
       <c r="F6" t="n">
-        <v>544322.4884839379</v>
+        <v>541985.7805722406</v>
       </c>
       <c r="G6" t="n">
-        <v>545778.0450930872</v>
+        <v>543441.3371813893</v>
       </c>
       <c r="H6" t="n">
-        <v>547235.6219317485</v>
+        <v>544898.9140200517</v>
       </c>
       <c r="I6" t="n">
-        <v>548695.2335713354</v>
+        <v>546358.5256596381</v>
       </c>
       <c r="J6" t="n">
-        <v>234636.8947742276</v>
+        <v>232300.1868625297</v>
       </c>
       <c r="K6" t="n">
-        <v>551620.6204974167</v>
+        <v>549283.912585719</v>
       </c>
       <c r="L6" t="n">
-        <v>553086.4258962332</v>
+        <v>550749.7179845357</v>
       </c>
       <c r="M6" t="n">
-        <v>381305.2617572347</v>
+        <v>379563.4119441266</v>
       </c>
       <c r="N6" t="n">
-        <v>544518.1587920884</v>
+        <v>542776.308978981</v>
       </c>
       <c r="O6" t="n">
-        <v>366485.8980498257</v>
+        <v>364744.0482367183</v>
       </c>
       <c r="P6" t="n">
-        <v>548456.5009008363</v>
+        <v>546714.6510877284</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>225</v>
@@ -27002,7 +27002,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>125</v>
@@ -27033,22 +27033,22 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
         <v>-0</v>
@@ -27112,7 +27112,7 @@
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27451,7 +27451,7 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
@@ -27502,7 +27502,7 @@
         <v>400</v>
       </c>
       <c r="Y2" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -27521,16 +27521,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>329.8300674532674</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27566,10 +27566,10 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>20.35776521751382</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>94.99587548954275</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27591,28 +27591,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>360.6832422535806</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
         <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>400</v>
@@ -27645,7 +27645,7 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>378.563614494389</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
@@ -27660,7 +27660,7 @@
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27755,16 +27755,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>155.587840727184</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -27794,16 +27794,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>81.5639999646113</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>33.78964074244533</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27828,34 +27828,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>376.1654965030195</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T7" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U7" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V7" t="n">
+        <v>359.4505875674658</v>
+      </c>
+      <c r="W7" t="n">
         <v>400</v>
       </c>
-      <c r="T7" t="n">
+      <c r="X7" t="n">
         <v>400</v>
       </c>
-      <c r="U7" t="n">
+      <c r="Y7" t="n">
         <v>400</v>
-      </c>
-      <c r="V7" t="n">
-        <v>400</v>
-      </c>
-      <c r="W7" t="n">
-        <v>226.3728098387097</v>
-      </c>
-      <c r="X7" t="n">
-        <v>247.4436454301076</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>235.8685316061257</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28040,13 +28040,13 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>20.35776521751382</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>15.21035976018675</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>306.7062506388766</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28074,10 +28074,10 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>301.650008079599</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
         <v>245.04387284153</v>
@@ -28086,13 +28086,13 @@
         <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>400</v>
       </c>
       <c r="K10" t="n">
-        <v>369.3176906843232</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,13 +28116,13 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
@@ -28134,7 +28134,7 @@
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28159,7 +28159,7 @@
         <v>225</v>
       </c>
       <c r="G11" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="H11" t="n">
         <v>225</v>
@@ -28213,7 +28213,7 @@
         <v>225</v>
       </c>
       <c r="Y11" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12">
@@ -28256,13 +28256,13 @@
         <v>225</v>
       </c>
       <c r="M12" t="n">
-        <v>225</v>
+        <v>19.11687125883903</v>
       </c>
       <c r="N12" t="n">
         <v>225</v>
       </c>
       <c r="O12" t="n">
-        <v>19.11687125883898</v>
+        <v>225</v>
       </c>
       <c r="P12" t="n">
         <v>225</v>
@@ -28429,13 +28429,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S14" t="n">
         <v>225</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>219.50680744288</v>
       </c>
       <c r="U14" t="n">
         <v>225</v>
@@ -28481,10 +28481,10 @@
         <v>225</v>
       </c>
       <c r="I15" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J15" t="n">
-        <v>225</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K15" t="n">
         <v>225</v>
@@ -28496,7 +28496,7 @@
         <v>225</v>
       </c>
       <c r="N15" t="n">
-        <v>26.99048536749072</v>
+        <v>225</v>
       </c>
       <c r="O15" t="n">
         <v>225</v>
@@ -28639,7 +28639,7 @@
         <v>225</v>
       </c>
       <c r="I17" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="S17" t="n">
         <v>225</v>
@@ -28733,13 +28733,13 @@
         <v>225</v>
       </c>
       <c r="N18" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O18" t="n">
         <v>225</v>
       </c>
       <c r="P18" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q18" t="n">
         <v>225</v>
@@ -28870,7 +28870,7 @@
         <v>225</v>
       </c>
       <c r="G20" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="H20" t="n">
         <v>225</v>
@@ -28924,7 +28924,7 @@
         <v>225</v>
       </c>
       <c r="Y20" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
     </row>
     <row r="21">
@@ -28967,7 +28967,7 @@
         <v>225</v>
       </c>
       <c r="M21" t="n">
-        <v>19.11687125883903</v>
+        <v>225</v>
       </c>
       <c r="N21" t="n">
         <v>225</v>
@@ -28976,7 +28976,7 @@
         <v>225</v>
       </c>
       <c r="P21" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q21" t="n">
         <v>225</v>
@@ -29101,13 +29101,13 @@
         <v>225</v>
       </c>
       <c r="E23" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="F23" t="n">
         <v>225</v>
       </c>
       <c r="G23" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="H23" t="n">
         <v>225</v>
@@ -29207,13 +29207,13 @@
         <v>225</v>
       </c>
       <c r="N24" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O24" t="n">
         <v>225</v>
       </c>
       <c r="P24" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q24" t="n">
         <v>225</v>
@@ -29350,7 +29350,7 @@
         <v>225</v>
       </c>
       <c r="I26" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29380,7 +29380,7 @@
         <v>225</v>
       </c>
       <c r="S26" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="T26" t="n">
         <v>225</v>
@@ -29429,13 +29429,13 @@
         <v>225</v>
       </c>
       <c r="I27" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
-        <v>225</v>
+        <v>78.91122027701098</v>
       </c>
       <c r="K27" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="L27" t="n">
         <v>225</v>
@@ -29453,7 +29453,7 @@
         <v>225</v>
       </c>
       <c r="Q27" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R27" t="n">
         <v>225</v>
@@ -29587,7 +29587,7 @@
         <v>225</v>
       </c>
       <c r="I29" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="S29" t="n">
         <v>225</v>
@@ -29681,13 +29681,13 @@
         <v>225</v>
       </c>
       <c r="N30" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="O30" t="n">
         <v>225</v>
       </c>
       <c r="P30" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q30" t="n">
         <v>225</v>
@@ -29824,7 +29824,7 @@
         <v>225</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S32" t="n">
         <v>225</v>
@@ -29903,10 +29903,10 @@
         <v>225</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J33" t="n">
-        <v>26.99048536749061</v>
+        <v>225</v>
       </c>
       <c r="K33" t="n">
         <v>225</v>
@@ -29915,7 +29915,7 @@
         <v>225</v>
       </c>
       <c r="M33" t="n">
-        <v>225</v>
+        <v>19.11687125883903</v>
       </c>
       <c r="N33" t="n">
         <v>225</v>
@@ -30091,7 +30091,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T35" t="n">
         <v>350</v>
@@ -30100,7 +30100,7 @@
         <v>350</v>
       </c>
       <c r="V35" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="W35" t="n">
         <v>350</v>
@@ -30119,7 +30119,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C36" t="n">
         <v>350</v>
@@ -30167,7 +30167,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="S36" t="n">
         <v>350</v>
@@ -30179,13 +30179,13 @@
         <v>350</v>
       </c>
       <c r="V36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>350</v>
       </c>
       <c r="X36" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="Y36" t="n">
         <v>350</v>
@@ -30292,7 +30292,7 @@
         <v>350</v>
       </c>
       <c r="G38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H38" t="n">
         <v>350</v>
@@ -30334,7 +30334,7 @@
         <v>350</v>
       </c>
       <c r="U38" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="V38" t="n">
         <v>350</v>
@@ -30362,10 +30362,10 @@
         <v>350</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>277.9320215941727</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -30374,10 +30374,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>136.6167105523271</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30453,7 +30453,7 @@
         <v>350</v>
       </c>
       <c r="H40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="I40" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30532,7 +30532,7 @@
         <v>350</v>
       </c>
       <c r="H41" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I41" t="n">
         <v>150.0811596826846</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30593,7 +30593,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C42" t="n">
         <v>350</v>
@@ -30608,10 +30608,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>325.7395358750273</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H42" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>217.1263858913485</v>
@@ -30662,7 +30662,7 @@
         <v>350</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43">
@@ -30726,10 +30726,10 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
+        <v>342.2113306341342</v>
+      </c>
+      <c r="U43" t="n">
         <v>350</v>
-      </c>
-      <c r="U43" t="n">
-        <v>342.2113306341342</v>
       </c>
       <c r="V43" t="n">
         <v>350</v>
@@ -30842,10 +30842,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>252.6980156874616</v>
       </c>
       <c r="G45" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>332.1680871864211</v>
@@ -30893,10 +30893,10 @@
         <v>350</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="X45" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="Y45" t="n">
         <v>350</v>
@@ -34877,28 +34877,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>79.70233741662405</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>364.7310511640923</v>
@@ -34931,7 +34931,7 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>168.5390479881313</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
@@ -34946,7 +34946,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,22 +34980,22 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
+        <v>384.9999999999999</v>
+      </c>
+      <c r="L5" t="n">
+        <v>369.4444444444443</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>385</v>
-      </c>
-      <c r="L5" t="n">
-        <v>369.4444444444445</v>
-      </c>
-      <c r="M5" t="n">
-        <v>385</v>
-      </c>
-      <c r="N5" t="n">
-        <v>385</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -35114,34 +35114,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>147.3943704014009</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>160.2802773512497</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,19 +35217,19 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>385</v>
       </c>
-      <c r="K8" t="n">
-        <v>384.9999999999999</v>
-      </c>
       <c r="L8" t="n">
+        <v>385</v>
+      </c>
+      <c r="M8" t="n">
         <v>369.4444444444443</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>385</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -35360,10 +35360,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>20.66910324264245</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -35372,13 +35372,13 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
         <v>364.7310511640923</v>
       </c>
       <c r="K10" t="n">
-        <v>80.79691688318015</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,13 +35402,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
@@ -35420,7 +35420,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35457,10 +35457,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>663.2638692218004</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,13 +35469,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>962.6692363858147</v>
+        <v>420.1280631196846</v>
       </c>
       <c r="P11" t="n">
-        <v>870.2908726334418</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35542,13 +35542,13 @@
         <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233433</v>
       </c>
       <c r="N12" t="n">
         <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
-        <v>260.5738931615854</v>
+        <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
         <v>338.6660045146532</v>
@@ -35697,7 +35697,7 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L14" t="n">
-        <v>916.1914086561842</v>
+        <v>373.6502353900541</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,7 +35706,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>420.1280631196846</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35767,10 +35767,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J15" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K15" t="n">
         <v>416.1038546407913</v>
@@ -35782,7 +35782,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>161.6170354761456</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O15" t="n">
         <v>466.4570219027464</v>
@@ -35928,25 +35928,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L17" t="n">
         <v>916.1914086561842</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>461.1078387353245</v>
+        <v>420.1280631196846</v>
       </c>
       <c r="P17" t="n">
-        <v>870.2908726334418</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36019,13 +36019,13 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N18" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O18" t="n">
         <v>466.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q18" t="n">
         <v>51.92073490952041</v>
@@ -36168,7 +36168,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230996</v>
+        <v>174.3339442569695</v>
       </c>
       <c r="L20" t="n">
         <v>916.1914086561842</v>
@@ -36180,7 +36180,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>420.1280631196846</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36253,7 +36253,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>106.0669134233433</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N21" t="n">
         <v>359.6265501086548</v>
@@ -36262,7 +36262,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q21" t="n">
         <v>51.92073490952041</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>663.2638692218004</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,13 +36417,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>815.3897934607513</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36493,13 +36493,13 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O24" t="n">
         <v>466.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q24" t="n">
         <v>51.92073490952041</v>
@@ -36642,7 +36642,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230996</v>
+        <v>617.3633331990579</v>
       </c>
       <c r="L26" t="n">
         <v>916.1914086561842</v>
@@ -36651,16 +36651,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>169.2516549051956</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P26" t="n">
-        <v>870.2908726334418</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36715,13 +36715,13 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>350.2086062376757</v>
+        <v>204.1198265146867</v>
       </c>
       <c r="K27" t="n">
-        <v>210.2207258996305</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
         <v>499.091375348687</v>
@@ -36739,7 +36739,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q27" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36879,16 +36879,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>122.773827175565</v>
+        <v>663.2638692218004</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
         <v>962.6692363858147</v>
@@ -36897,7 +36897,7 @@
         <v>870.2908726334418</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36967,13 +36967,13 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>153.743421367494</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O30" t="n">
         <v>466.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q30" t="n">
         <v>51.92073490952041</v>
@@ -37116,10 +37116,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>916.1914086561842</v>
+        <v>663.2638692218004</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
@@ -37128,13 +37128,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>420.1280631196846</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,10 +37189,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J33" t="n">
-        <v>152.1990916051663</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K33" t="n">
         <v>416.1038546407913</v>
@@ -37201,7 +37201,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M33" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233433</v>
       </c>
       <c r="N33" t="n">
         <v>359.6265501086548</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="K35" t="n">
         <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>536.4141414141417</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37587,13 +37587,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>20.40522350612643</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>516.0089179080152</v>
@@ -37602,7 +37602,7 @@
         <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>20.40522350612631</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37739,7 +37739,7 @@
         <v>104.95612715847</v>
       </c>
       <c r="H40" t="n">
-        <v>121.2288738983814</v>
+        <v>113.4402045325156</v>
       </c>
       <c r="I40" t="n">
         <v>173.3665443798817</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37824,16 +37824,16 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>93.38475247205329</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L41" t="n">
         <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
         <v>559</v>
@@ -38012,10 +38012,10 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U43" t="n">
-        <v>191.2529393596762</v>
+        <v>199.0416087255421</v>
       </c>
       <c r="V43" t="n">
         <v>150.8296897837838</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>93.38475247205329</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
@@ -38070,10 +38070,10 @@
         <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="N44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
